--- a/LABELS.xlsx
+++ b/LABELS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2025/Drucken/Section Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{A57D7E76-FB01-A74A-94BB-42D54020D4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7303F045-E800-3C48-960B-B0BC3723AB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1830" windowWidth="23040" windowHeight="7338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3725" uniqueCount="1428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3728" uniqueCount="1428">
   <si>
     <t>Katalog-Nr</t>
   </si>
@@ -5215,6 +5215,9 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
@@ -5280,6 +5283,9 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
       <c r="B10" t="s">
         <v>46</v>
       </c>
@@ -5531,6 +5537,9 @@
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
       <c r="B14" t="s">
         <v>149</v>
       </c>

--- a/LABELS.xlsx
+++ b/LABELS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2025/Drucken/Section Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7303F045-E800-3C48-960B-B0BC3723AB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE426A90-35EB-264F-968B-8DBAD6D3B36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1830" windowWidth="23040" windowHeight="7338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3728" uniqueCount="1428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3805" uniqueCount="1428">
   <si>
     <t>Katalog-Nr</t>
   </si>
@@ -4325,10 +4325,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4372,14 +4380,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4896,6 +4907,9 @@
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
       <c r="B4" t="s">
         <v>48</v>
       </c>
@@ -4961,6 +4975,9 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
@@ -5088,6 +5105,9 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
       <c r="B7" t="s">
         <v>84</v>
       </c>
@@ -5345,6 +5365,9 @@
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
       <c r="B11" t="s">
         <v>125</v>
       </c>
@@ -5410,6 +5433,9 @@
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
       <c r="B12" t="s">
         <v>119</v>
       </c>
@@ -5728,7 +5754,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>177</v>
       </c>
@@ -5793,7 +5819,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>189</v>
       </c>
@@ -5852,7 +5878,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
       <c r="B19" t="s">
         <v>196</v>
       </c>
@@ -5917,7 +5946,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>209</v>
       </c>
@@ -5982,7 +6011,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>214</v>
       </c>
@@ -6047,7 +6076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>223</v>
       </c>
@@ -6106,7 +6135,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>229</v>
       </c>
@@ -6165,7 +6194,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>239</v>
       </c>
@@ -6227,7 +6256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>244</v>
       </c>
@@ -6292,7 +6321,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
       <c r="B26" t="s">
         <v>249</v>
       </c>
@@ -6357,7 +6389,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
       <c r="B27" t="s">
         <v>258</v>
       </c>
@@ -6422,7 +6457,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
       <c r="B28" t="s">
         <v>269</v>
       </c>
@@ -6487,7 +6525,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>282</v>
       </c>
@@ -6549,7 +6587,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>292</v>
       </c>
@@ -6608,7 +6646,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
       <c r="B31" t="s">
         <v>303</v>
       </c>
@@ -6673,7 +6714,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>308</v>
       </c>
@@ -6738,7 +6779,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>318</v>
       </c>
@@ -6803,7 +6844,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>324</v>
       </c>
@@ -6868,7 +6909,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
       <c r="B35" t="s">
         <v>328</v>
       </c>
@@ -6933,7 +6977,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>333</v>
       </c>
@@ -6992,7 +7036,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
       <c r="B37" t="s">
         <v>338</v>
       </c>
@@ -7057,7 +7104,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>342</v>
       </c>
@@ -7122,7 +7169,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>351</v>
       </c>
@@ -7187,7 +7234,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>363</v>
       </c>
@@ -7246,7 +7293,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>31</v>
+      </c>
       <c r="B41" t="s">
         <v>374</v>
       </c>
@@ -7314,7 +7364,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>382</v>
       </c>
@@ -7379,7 +7429,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>389</v>
       </c>
@@ -7438,7 +7488,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>394</v>
       </c>
@@ -7497,7 +7547,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>400</v>
       </c>
@@ -7556,7 +7606,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
       <c r="B46" t="s">
         <v>406</v>
       </c>
@@ -7621,7 +7674,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>411</v>
       </c>
@@ -7686,7 +7739,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>416</v>
       </c>
@@ -7745,7 +7798,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>420</v>
       </c>
@@ -7804,7 +7857,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
         <v>425</v>
       </c>
@@ -7869,7 +7922,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>430</v>
       </c>
@@ -7928,7 +7981,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>31</v>
+      </c>
       <c r="B52" t="s">
         <v>437</v>
       </c>
@@ -7993,7 +8049,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>443</v>
       </c>
@@ -8058,7 +8114,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>454</v>
       </c>
@@ -8123,7 +8179,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
       <c r="B55" t="s">
         <v>459</v>
       </c>
@@ -8188,7 +8247,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>465</v>
       </c>
@@ -8247,7 +8306,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>469</v>
       </c>
@@ -8315,7 +8374,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>31</v>
+      </c>
       <c r="B58" t="s">
         <v>481</v>
       </c>
@@ -8380,7 +8442,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>31</v>
+      </c>
       <c r="B59" t="s">
         <v>491</v>
       </c>
@@ -8448,7 +8513,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>31</v>
+      </c>
       <c r="B60" t="s">
         <v>497</v>
       </c>
@@ -8507,7 +8575,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>31</v>
+      </c>
       <c r="B61" t="s">
         <v>509</v>
       </c>
@@ -8575,7 +8646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>515</v>
       </c>
@@ -8640,7 +8711,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>31</v>
+      </c>
       <c r="B63" t="s">
         <v>525</v>
       </c>
@@ -8705,7 +8779,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>31</v>
+      </c>
       <c r="B64" t="s">
         <v>536</v>
       </c>
@@ -8770,7 +8847,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>547</v>
       </c>
@@ -8835,7 +8912,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>31</v>
+      </c>
       <c r="B66" t="s">
         <v>552</v>
       </c>
@@ -8900,7 +8980,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>31</v>
+      </c>
       <c r="B67" t="s">
         <v>563</v>
       </c>
@@ -8959,7 +9042,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
         <v>569</v>
       </c>
@@ -9018,7 +9101,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>31</v>
+      </c>
       <c r="B69" t="s">
         <v>579</v>
       </c>
@@ -9080,7 +9166,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>31</v>
+      </c>
       <c r="B70" t="s">
         <v>590</v>
       </c>
@@ -9148,7 +9237,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
         <v>596</v>
       </c>
@@ -9213,7 +9302,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>31</v>
+      </c>
       <c r="B72" t="s">
         <v>602</v>
       </c>
@@ -9278,7 +9370,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
         <v>607</v>
       </c>
@@ -9343,7 +9435,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>31</v>
+      </c>
       <c r="B74" t="s">
         <v>618</v>
       </c>
@@ -9408,7 +9503,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>31</v>
+      </c>
       <c r="B75" t="s">
         <v>624</v>
       </c>
@@ -9467,7 +9565,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>31</v>
+      </c>
       <c r="B76" t="s">
         <v>629</v>
       </c>
@@ -9526,7 +9627,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>31</v>
+      </c>
       <c r="B77" t="s">
         <v>640</v>
       </c>
@@ -9591,7 +9695,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
         <v>651</v>
       </c>
@@ -9656,7 +9760,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
         <v>656</v>
       </c>
@@ -9721,7 +9825,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
         <v>664</v>
       </c>
@@ -9786,7 +9890,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
         <v>670</v>
       </c>
@@ -9851,7 +9955,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>31</v>
+      </c>
       <c r="B82" t="s">
         <v>675</v>
       </c>
@@ -9913,7 +10020,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>31</v>
+      </c>
       <c r="B83" t="s">
         <v>681</v>
       </c>
@@ -9978,7 +10088,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
         <v>692</v>
       </c>
@@ -10037,7 +10147,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
         <v>699</v>
       </c>
@@ -10102,7 +10212,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>31</v>
+      </c>
       <c r="B86" t="s">
         <v>704</v>
       </c>
@@ -10167,7 +10280,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
         <v>709</v>
       </c>
@@ -10232,7 +10345,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
         <v>721</v>
       </c>
@@ -10291,7 +10404,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
         <v>730</v>
       </c>
@@ -10356,7 +10469,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
         <v>740</v>
       </c>
@@ -10421,7 +10534,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
         <v>745</v>
       </c>
@@ -10486,7 +10599,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>31</v>
+      </c>
       <c r="B92" t="s">
         <v>755</v>
       </c>
@@ -10551,7 +10667,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>31</v>
+      </c>
       <c r="B93" t="s">
         <v>760</v>
       </c>
@@ -10616,7 +10735,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
         <v>770</v>
       </c>
@@ -10681,7 +10800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
         <v>776</v>
       </c>
@@ -10746,7 +10865,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
         <v>781</v>
       </c>
@@ -10811,7 +10930,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>31</v>
+      </c>
       <c r="B97" t="s">
         <v>786</v>
       </c>
@@ -10876,7 +10998,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
         <v>790</v>
       </c>
@@ -10935,7 +11057,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>31</v>
+      </c>
       <c r="B99" t="s">
         <v>795</v>
       </c>
@@ -11000,7 +11125,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="100" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
         <v>804</v>
       </c>
@@ -11065,7 +11190,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="101" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>31</v>
+      </c>
       <c r="B101" t="s">
         <v>816</v>
       </c>
@@ -11130,7 +11258,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="102" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
         <v>826</v>
       </c>
@@ -11189,7 +11317,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
         <v>836</v>
       </c>
@@ -11248,7 +11376,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="104" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>31</v>
+      </c>
       <c r="B104" t="s">
         <v>841</v>
       </c>
@@ -11313,7 +11444,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="105" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>31</v>
+      </c>
       <c r="B105" t="s">
         <v>846</v>
       </c>
@@ -11378,7 +11512,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="106" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>31</v>
+      </c>
       <c r="B106" t="s">
         <v>856</v>
       </c>
@@ -11446,7 +11583,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
         <v>861</v>
       </c>
@@ -11505,7 +11642,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
         <v>866</v>
       </c>
@@ -11564,7 +11701,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
         <v>878</v>
       </c>
@@ -11629,7 +11766,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="110" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
         <v>889</v>
       </c>
@@ -11694,7 +11831,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="111" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>31</v>
+      </c>
       <c r="B111" t="s">
         <v>900</v>
       </c>
@@ -11762,7 +11902,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>31</v>
+      </c>
       <c r="B112" t="s">
         <v>910</v>
       </c>
@@ -11827,7 +11970,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>31</v>
+      </c>
       <c r="B113" t="s">
         <v>920</v>
       </c>
@@ -11892,7 +12038,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
         <v>930</v>
       </c>
@@ -11951,7 +12097,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="115" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
         <v>941</v>
       </c>
@@ -12010,7 +12156,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="116" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
         <v>952</v>
       </c>
@@ -12069,7 +12215,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
         <v>962</v>
       </c>
@@ -12134,7 +12280,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="118" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
         <v>972</v>
       </c>
@@ -12196,7 +12342,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="119" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
         <v>982</v>
       </c>
@@ -12255,7 +12401,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="120" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
         <v>987</v>
       </c>
@@ -12314,7 +12460,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="121" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
         <v>992</v>
       </c>
@@ -12373,7 +12519,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
         <v>995</v>
       </c>
@@ -12438,7 +12584,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="123" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
         <v>1005</v>
       </c>
@@ -12503,7 +12649,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="124" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
         <v>1013</v>
       </c>
@@ -12568,7 +12714,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
         <v>1023</v>
       </c>
@@ -12633,7 +12779,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>31</v>
+      </c>
       <c r="B126" t="s">
         <v>1028</v>
       </c>
@@ -12698,7 +12847,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
         <v>1038</v>
       </c>
@@ -12763,7 +12912,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
         <v>1043</v>
       </c>
@@ -12822,7 +12971,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="129" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B129" t="s">
         <v>1049</v>
       </c>
@@ -12881,7 +13030,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="130" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>31</v>
+      </c>
       <c r="B130" t="s">
         <v>1054</v>
       </c>
@@ -12946,7 +13098,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="131" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>31</v>
+      </c>
       <c r="B131" t="s">
         <v>1060</v>
       </c>
@@ -13005,7 +13160,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
         <v>1065</v>
       </c>
@@ -13070,7 +13225,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="133" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
         <v>1070</v>
       </c>
@@ -13135,7 +13290,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="134" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
         <v>1074</v>
       </c>
@@ -13194,7 +13349,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>31</v>
+      </c>
       <c r="B135" t="s">
         <v>1079</v>
       </c>
@@ -13259,7 +13417,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="136" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B136" t="s">
         <v>1088</v>
       </c>
@@ -13324,7 +13482,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B137" t="s">
         <v>1093</v>
       </c>
@@ -13383,7 +13541,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="138" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>31</v>
+      </c>
       <c r="B138" t="s">
         <v>1104</v>
       </c>
@@ -13445,7 +13606,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="139" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>31</v>
+      </c>
       <c r="B139" t="s">
         <v>1115</v>
       </c>
@@ -13507,7 +13671,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="140" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>31</v>
+      </c>
       <c r="B140" t="s">
         <v>1125</v>
       </c>
@@ -13569,7 +13736,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="141" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
         <v>1130</v>
       </c>
@@ -13631,7 +13798,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="142" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>31</v>
+      </c>
       <c r="B142" t="s">
         <v>1135</v>
       </c>
@@ -13693,7 +13863,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="143" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
         <v>1139</v>
       </c>
@@ -13755,7 +13925,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="144" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B144" t="s">
         <v>1144</v>
       </c>
@@ -13814,7 +13984,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="145" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>31</v>
+      </c>
       <c r="B145" t="s">
         <v>1155</v>
       </c>
@@ -13882,7 +14055,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="146" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>31</v>
+      </c>
       <c r="B146" t="s">
         <v>1160</v>
       </c>
@@ -13941,7 +14117,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="147" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>31</v>
+      </c>
       <c r="B147" t="s">
         <v>1165</v>
       </c>
@@ -14003,7 +14182,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="148" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>31</v>
+      </c>
       <c r="B148" t="s">
         <v>1176</v>
       </c>
@@ -14068,7 +14250,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="149" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>31</v>
+      </c>
       <c r="B149" t="s">
         <v>1181</v>
       </c>
@@ -14133,7 +14318,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="150" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>31</v>
+      </c>
       <c r="B150" t="s">
         <v>1186</v>
       </c>
@@ -14195,7 +14383,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="151" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>31</v>
+      </c>
       <c r="B151" t="s">
         <v>1191</v>
       </c>
@@ -14260,7 +14451,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="152" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
         <v>1201</v>
       </c>
@@ -14325,7 +14516,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="153" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B153" t="s">
         <v>1207</v>
       </c>
@@ -14384,7 +14575,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="154" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B154" t="s">
         <v>1218</v>
       </c>
@@ -14443,7 +14634,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="155" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B155" t="s">
         <v>1228</v>
       </c>
@@ -14502,7 +14693,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="156" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>31</v>
+      </c>
       <c r="B156" t="s">
         <v>1233</v>
       </c>
@@ -14561,7 +14755,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="157" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>31</v>
+      </c>
       <c r="B157" t="s">
         <v>1244</v>
       </c>
@@ -14626,7 +14823,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="158" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>31</v>
+      </c>
       <c r="B158" t="s">
         <v>1254</v>
       </c>
@@ -14685,7 +14885,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="159" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>31</v>
+      </c>
       <c r="B159" t="s">
         <v>1265</v>
       </c>
@@ -14753,7 +14956,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="160" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>31</v>
+      </c>
       <c r="B160" t="s">
         <v>1275</v>
       </c>
@@ -14818,7 +15024,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="161" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>31</v>
+      </c>
       <c r="B161" t="s">
         <v>1280</v>
       </c>
@@ -14877,7 +15086,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>31</v>
+      </c>
       <c r="B162" t="s">
         <v>1286</v>
       </c>
@@ -14936,7 +15148,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="163" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>31</v>
+      </c>
       <c r="B163" t="s">
         <v>1296</v>
       </c>
@@ -14998,7 +15213,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="164" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B164" t="s">
         <v>1302</v>
       </c>
@@ -15063,7 +15278,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="165" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>31</v>
+      </c>
       <c r="B165" t="s">
         <v>1310</v>
       </c>
@@ -15128,7 +15346,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="166" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>31</v>
+      </c>
       <c r="B166" t="s">
         <v>1314</v>
       </c>
@@ -15193,7 +15414,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="167" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B167" t="s">
         <v>1319</v>
       </c>
@@ -15258,7 +15479,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B168" t="s">
         <v>1323</v>
       </c>
@@ -15317,7 +15538,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="169" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>31</v>
+      </c>
       <c r="B169" t="s">
         <v>1333</v>
       </c>
@@ -15376,7 +15600,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="170" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B170" t="s">
         <v>1339</v>
       </c>
@@ -15435,7 +15659,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="171" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>31</v>
+      </c>
       <c r="B171" t="s">
         <v>1344</v>
       </c>
@@ -15500,7 +15727,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="172" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B172" t="s">
         <v>1350</v>
       </c>
@@ -15565,7 +15792,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="173" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B173" t="s">
         <v>1361</v>
       </c>
@@ -15630,7 +15857,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="174" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>31</v>
+      </c>
       <c r="B174" t="s">
         <v>1368</v>
       </c>
@@ -15695,7 +15925,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="175" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>31</v>
+      </c>
       <c r="B175" t="s">
         <v>1373</v>
       </c>
@@ -15760,7 +15993,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="176" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B176" t="s">
         <v>1378</v>
       </c>
@@ -15825,7 +16058,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="177" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>31</v>
+      </c>
       <c r="B177" t="s">
         <v>1387</v>
       </c>
@@ -15890,7 +16126,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="178" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>31</v>
+      </c>
       <c r="B178" t="s">
         <v>1391</v>
       </c>
@@ -15949,7 +16188,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="179" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B179" t="s">
         <v>1401</v>
       </c>
@@ -16014,7 +16253,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="180" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>31</v>
+      </c>
       <c r="B180" t="s">
         <v>1405</v>
       </c>
@@ -16076,7 +16318,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="181" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B181" t="s">
         <v>1410</v>
       </c>
@@ -16135,7 +16377,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="182" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B182" t="s">
         <v>1415</v>
       </c>
@@ -16194,7 +16436,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B183" t="s">
         <v>1420</v>
       </c>
